--- a/vocabulary_database_template.xlsx
+++ b/vocabulary_database_template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="1210">
   <si>
     <t>ID</t>
   </si>
@@ -339,6 +339,3318 @@
   </si>
   <si>
     <t>Nhập từ vựng để convert sang data.js</t>
+  </si>
+  <si>
+    <t>Gia đình</t>
+  </si>
+  <si>
+    <t>이것은 제 가족입니다。</t>
+  </si>
+  <si>
+    <t>bố</t>
+  </si>
+  <si>
+    <t>父</t>
+  </si>
+  <si>
+    <t>ちち</t>
+  </si>
+  <si>
+    <t>father</t>
+  </si>
+  <si>
+    <t>/ˈfɑːðər/</t>
+  </si>
+  <si>
+    <t>爸爸</t>
+  </si>
+  <si>
+    <t>bàba</t>
+  </si>
+  <si>
+    <t>아버지</t>
+  </si>
+  <si>
+    <t>abeoji</t>
+  </si>
+  <si>
+    <t>Bố tôi rất vui tính.</t>
+  </si>
+  <si>
+    <t>父はとても明るいです。</t>
+  </si>
+  <si>
+    <t>My father is very cheerful.</t>
+  </si>
+  <si>
+    <t>我爸爸很开朗。</t>
+  </si>
+  <si>
+    <t>아버지는 아주 밝으십니다。</t>
+  </si>
+  <si>
+    <t>mẹ</t>
+  </si>
+  <si>
+    <t>母</t>
+  </si>
+  <si>
+    <t>はは</t>
+  </si>
+  <si>
+    <t>mother</t>
+  </si>
+  <si>
+    <t>/ˈmʌðər/</t>
+  </si>
+  <si>
+    <t>妈妈</t>
+  </si>
+  <si>
+    <t>māma</t>
+  </si>
+  <si>
+    <t>어머니</t>
+  </si>
+  <si>
+    <t>eomeoni</t>
+  </si>
+  <si>
+    <t>Mẹ tôi nấu ăn rất ngon.</t>
+  </si>
+  <si>
+    <t>母は料理がとても上手です。</t>
+  </si>
+  <si>
+    <t>My mother cooks very well.</t>
+  </si>
+  <si>
+    <t>我妈妈做饭很好吃。</t>
+  </si>
+  <si>
+    <t>어머니는 요리를 아주 잘하십니다。</t>
+  </si>
+  <si>
+    <t>anh trai</t>
+  </si>
+  <si>
+    <t>兄</t>
+  </si>
+  <si>
+    <t>あに</t>
+  </si>
+  <si>
+    <t>older brother</t>
+  </si>
+  <si>
+    <t>/ˌoʊldər ˈbrʌðər/</t>
+  </si>
+  <si>
+    <t>哥哥</t>
+  </si>
+  <si>
+    <t>gēge</t>
+  </si>
+  <si>
+    <t>형</t>
+  </si>
+  <si>
+    <t>hyeong</t>
+  </si>
+  <si>
+    <t>Anh trai tôi thích thể thao.</t>
+  </si>
+  <si>
+    <t>兄はスポーツが好きです。</t>
+  </si>
+  <si>
+    <t>My older brother likes sports.</t>
+  </si>
+  <si>
+    <t>我哥哥喜欢运动。</t>
+  </si>
+  <si>
+    <t>형은 운동을 좋아합니다。</t>
+  </si>
+  <si>
+    <t>chị gái</t>
+  </si>
+  <si>
+    <t>姉</t>
+  </si>
+  <si>
+    <t>あね</t>
+  </si>
+  <si>
+    <t>older sister</t>
+  </si>
+  <si>
+    <t>/ˌoʊldər ˈsɪstər/</t>
+  </si>
+  <si>
+    <t>姐姐</t>
+  </si>
+  <si>
+    <t>jiějie</t>
+  </si>
+  <si>
+    <t>누나</t>
+  </si>
+  <si>
+    <t>nuna</t>
+  </si>
+  <si>
+    <t>Chị gái tôi hay cười.</t>
+  </si>
+  <si>
+    <t>姉はよく笑います。</t>
+  </si>
+  <si>
+    <t>My older sister smiles a lot.</t>
+  </si>
+  <si>
+    <t>我姐姐常常笑。</t>
+  </si>
+  <si>
+    <t>누나는 자주 웃습니다。</t>
+  </si>
+  <si>
+    <t>em trai</t>
+  </si>
+  <si>
+    <t>弟</t>
+  </si>
+  <si>
+    <t>おとうと</t>
+  </si>
+  <si>
+    <t>younger brother</t>
+  </si>
+  <si>
+    <t>/ˌjʌŋɡər ˈbrʌðər/</t>
+  </si>
+  <si>
+    <t>弟弟</t>
+  </si>
+  <si>
+    <t>dìdi</t>
+  </si>
+  <si>
+    <t>남동생</t>
+  </si>
+  <si>
+    <t>namdongsaeng</t>
+  </si>
+  <si>
+    <t>Em trai tôi rất khỏe.</t>
+  </si>
+  <si>
+    <t>弟はとても元気です。</t>
+  </si>
+  <si>
+    <t>My younger brother is very energetic.</t>
+  </si>
+  <si>
+    <t>我弟弟很有精神。</t>
+  </si>
+  <si>
+    <t>남동생은 아주 활기찹니다。</t>
+  </si>
+  <si>
+    <t>em gái</t>
+  </si>
+  <si>
+    <t>妹</t>
+  </si>
+  <si>
+    <t>いもうと</t>
+  </si>
+  <si>
+    <t>younger sister</t>
+  </si>
+  <si>
+    <t>/ˌjʌŋɡər ˈsɪstər/</t>
+  </si>
+  <si>
+    <t>妹妹</t>
+  </si>
+  <si>
+    <t>mèimei</t>
+  </si>
+  <si>
+    <t>여동생</t>
+  </si>
+  <si>
+    <t>yeodongsaeng</t>
+  </si>
+  <si>
+    <t>Em gái tôi thích hát.</t>
+  </si>
+  <si>
+    <t>妹は歌うことが好きです。</t>
+  </si>
+  <si>
+    <t>My younger sister likes singing.</t>
+  </si>
+  <si>
+    <t>我妹妹喜欢唱歌。</t>
+  </si>
+  <si>
+    <t>여동생은 노래하는 것을 좋아합니다。</t>
+  </si>
+  <si>
+    <t>ông</t>
+  </si>
+  <si>
+    <t>祖父</t>
+  </si>
+  <si>
+    <t>そふ</t>
+  </si>
+  <si>
+    <t>grandfather</t>
+  </si>
+  <si>
+    <t>/ˈɡrændˌfɑːðər/</t>
+  </si>
+  <si>
+    <t>爷爷</t>
+  </si>
+  <si>
+    <t>yéye</t>
+  </si>
+  <si>
+    <t>할아버지</t>
+  </si>
+  <si>
+    <t>harabeoji</t>
+  </si>
+  <si>
+    <t>Ông tôi kể chuyện rất hay.</t>
+  </si>
+  <si>
+    <t>祖父は話がとても上手です。</t>
+  </si>
+  <si>
+    <t>My grandfather tells great stories.</t>
+  </si>
+  <si>
+    <t>我爷爷讲故事很好。</t>
+  </si>
+  <si>
+    <t>할아버지는 이야기를 아주 잘하십니다。</t>
+  </si>
+  <si>
+    <t>bà</t>
+  </si>
+  <si>
+    <t>祖母</t>
+  </si>
+  <si>
+    <t>そぼ</t>
+  </si>
+  <si>
+    <t>grandmother</t>
+  </si>
+  <si>
+    <t>/ˈɡrændˌmʌðər/</t>
+  </si>
+  <si>
+    <t>奶奶</t>
+  </si>
+  <si>
+    <t>nǎinai</t>
+  </si>
+  <si>
+    <t>할머니</t>
+  </si>
+  <si>
+    <t>halmeoni</t>
+  </si>
+  <si>
+    <t>Bà tôi rất hiền.</t>
+  </si>
+  <si>
+    <t>祖母はとても優しいです。</t>
+  </si>
+  <si>
+    <t>My grandmother is very kind.</t>
+  </si>
+  <si>
+    <t>我奶奶很温柔。</t>
+  </si>
+  <si>
+    <t>할머니는 아주 다정하십니다。</t>
+  </si>
+  <si>
+    <t>con</t>
+  </si>
+  <si>
+    <t>子ども</t>
+  </si>
+  <si>
+    <t>こども</t>
+  </si>
+  <si>
+    <t>child</t>
+  </si>
+  <si>
+    <t>/tʃaɪld/</t>
+  </si>
+  <si>
+    <t>孩子</t>
+  </si>
+  <si>
+    <t>háizi</t>
+  </si>
+  <si>
+    <t>아이</t>
+  </si>
+  <si>
+    <t>ai</t>
+  </si>
+  <si>
+    <t>Con tôi cười rất đáng yêu.</t>
+  </si>
+  <si>
+    <t>子どもはとてもかわいく笑います。</t>
+  </si>
+  <si>
+    <t>My child smiles very cutely.</t>
+  </si>
+  <si>
+    <t>我的孩子笑得很可爱。</t>
+  </si>
+  <si>
+    <t>아이는 아주 귀엽게 웃습니다。</t>
+  </si>
+  <si>
+    <t>ga tàu</t>
+  </si>
+  <si>
+    <t>駅</t>
+  </si>
+  <si>
+    <t>えき</t>
+  </si>
+  <si>
+    <t>station</t>
+  </si>
+  <si>
+    <t>/ˈsteɪʃən/</t>
+  </si>
+  <si>
+    <t>车站</t>
+  </si>
+  <si>
+    <t>chēzhàn</t>
+  </si>
+  <si>
+    <t>역</t>
+  </si>
+  <si>
+    <t>yeok</t>
+  </si>
+  <si>
+    <t>Tôi đang ở ga tàu.</t>
+  </si>
+  <si>
+    <t>私は駅にいます。</t>
+  </si>
+  <si>
+    <t>I am at the station.</t>
+  </si>
+  <si>
+    <t>我在车站。</t>
+  </si>
+  <si>
+    <t>저는 역에 있습니다.</t>
+  </si>
+  <si>
+    <t>vé</t>
+  </si>
+  <si>
+    <t>切符</t>
+  </si>
+  <si>
+    <t>きっぷ</t>
+  </si>
+  <si>
+    <t>ticket</t>
+  </si>
+  <si>
+    <t>/ˈtɪkɪt/</t>
+  </si>
+  <si>
+    <t>票</t>
+  </si>
+  <si>
+    <t>piào</t>
+  </si>
+  <si>
+    <t>표</t>
+  </si>
+  <si>
+    <t>pyo</t>
+  </si>
+  <si>
+    <t>Tôi đã mua vé.</t>
+  </si>
+  <si>
+    <t>切符を買いました。</t>
+  </si>
+  <si>
+    <t>I bought a ticket.</t>
+  </si>
+  <si>
+    <t>我买了票。</t>
+  </si>
+  <si>
+    <t>표를 샀습니다.</t>
+  </si>
+  <si>
+    <t>tàu điện</t>
+  </si>
+  <si>
+    <t>電車</t>
+  </si>
+  <si>
+    <t>でんしゃ</t>
+  </si>
+  <si>
+    <t>train</t>
+  </si>
+  <si>
+    <t>/treɪn/</t>
+  </si>
+  <si>
+    <t>火车</t>
+  </si>
+  <si>
+    <t>huǒchē</t>
+  </si>
+  <si>
+    <t>기차</t>
+  </si>
+  <si>
+    <t>gicha</t>
+  </si>
+  <si>
+    <t>Tôi đi tàu điện.</t>
+  </si>
+  <si>
+    <t>電車で行きます。</t>
+  </si>
+  <si>
+    <t>I go by train.</t>
+  </si>
+  <si>
+    <t>我坐火车去。</t>
+  </si>
+  <si>
+    <t>기차로 갑니다.</t>
+  </si>
+  <si>
+    <t>xe buýt</t>
+  </si>
+  <si>
+    <t>バス</t>
+  </si>
+  <si>
+    <t>ばす</t>
+  </si>
+  <si>
+    <t>bus</t>
+  </si>
+  <si>
+    <t>/bʌs/</t>
+  </si>
+  <si>
+    <t>公交车</t>
+  </si>
+  <si>
+    <t>gōngjiāochē</t>
+  </si>
+  <si>
+    <t>버스</t>
+  </si>
+  <si>
+    <t>beoseu</t>
+  </si>
+  <si>
+    <t>Tôi đi xe buýt.</t>
+  </si>
+  <si>
+    <t>バスで行きます。</t>
+  </si>
+  <si>
+    <t>I go by bus.</t>
+  </si>
+  <si>
+    <t>我坐公交车去。</t>
+  </si>
+  <si>
+    <t>버스로 갑니다.</t>
+  </si>
+  <si>
+    <t>bản đồ</t>
+  </si>
+  <si>
+    <t>地図</t>
+  </si>
+  <si>
+    <t>ちず</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>/mæp/</t>
+  </si>
+  <si>
+    <t>地图</t>
+  </si>
+  <si>
+    <t>dìtú</t>
+  </si>
+  <si>
+    <t>지도</t>
+  </si>
+  <si>
+    <t>jido</t>
+  </si>
+  <si>
+    <t>Bản đồ rất hữu ích.</t>
+  </si>
+  <si>
+    <t>地図は便利です。</t>
+  </si>
+  <si>
+    <t>The map is useful.</t>
+  </si>
+  <si>
+    <t>地图很有用。</t>
+  </si>
+  <si>
+    <t>지도는 유용합니다.</t>
+  </si>
+  <si>
+    <t>hành lý</t>
+  </si>
+  <si>
+    <t>荷物</t>
+  </si>
+  <si>
+    <t>にもつ</t>
+  </si>
+  <si>
+    <t>luggage</t>
+  </si>
+  <si>
+    <t>/ˈlʌɡɪdʒ/</t>
+  </si>
+  <si>
+    <t>行李</t>
+  </si>
+  <si>
+    <t>xíngli</t>
+  </si>
+  <si>
+    <t>짐</t>
+  </si>
+  <si>
+    <t>jim</t>
+  </si>
+  <si>
+    <t>Hành lý của tôi ở đây.</t>
+  </si>
+  <si>
+    <t>荷物はここです。</t>
+  </si>
+  <si>
+    <t>My luggage is here.</t>
+  </si>
+  <si>
+    <t>我的行李在这里。</t>
+  </si>
+  <si>
+    <t>제 짐은 여기 있습니다.</t>
+  </si>
+  <si>
+    <t>hộ chiếu</t>
+  </si>
+  <si>
+    <t>パスポート</t>
+  </si>
+  <si>
+    <t>ぱすぽーと</t>
+  </si>
+  <si>
+    <t>passport</t>
+  </si>
+  <si>
+    <t>/ˈpæspɔːrt/</t>
+  </si>
+  <si>
+    <t>护照</t>
+  </si>
+  <si>
+    <t>hùzhào</t>
+  </si>
+  <si>
+    <t>여권</t>
+  </si>
+  <si>
+    <t>yeogwon</t>
+  </si>
+  <si>
+    <t>Tôi mang theo hộ chiếu.</t>
+  </si>
+  <si>
+    <t>パスポートを持っています。</t>
+  </si>
+  <si>
+    <t>I have my passport.</t>
+  </si>
+  <si>
+    <t>我带着护照。</t>
+  </si>
+  <si>
+    <t>여권을 가지고 있습니다.</t>
+  </si>
+  <si>
+    <t>ảnh</t>
+  </si>
+  <si>
+    <t>写真</t>
+  </si>
+  <si>
+    <t>しゃしん</t>
+  </si>
+  <si>
+    <t>photo</t>
+  </si>
+  <si>
+    <t>/ˈfoʊtoʊ/</t>
+  </si>
+  <si>
+    <t>照片</t>
+  </si>
+  <si>
+    <t>zhàopiàn</t>
+  </si>
+  <si>
+    <t>사진</t>
+  </si>
+  <si>
+    <t>sajin</t>
+  </si>
+  <si>
+    <t>Tôi chụp một bức ảnh.</t>
+  </si>
+  <si>
+    <t>写真を撮ります。</t>
+  </si>
+  <si>
+    <t>I take a photo.</t>
+  </si>
+  <si>
+    <t>我拍照片。</t>
+  </si>
+  <si>
+    <t>사진을 찍습니다.</t>
+  </si>
+  <si>
+    <t>công viên</t>
+  </si>
+  <si>
+    <t>公園</t>
+  </si>
+  <si>
+    <t>こうえん</t>
+  </si>
+  <si>
+    <t>park</t>
+  </si>
+  <si>
+    <t>/pɑːrk/</t>
+  </si>
+  <si>
+    <t>公园</t>
+  </si>
+  <si>
+    <t>gōngyuán</t>
+  </si>
+  <si>
+    <t>공원</t>
+  </si>
+  <si>
+    <t>gongwon</t>
+  </si>
+  <si>
+    <t>Chúng tôi đi công viên.</t>
+  </si>
+  <si>
+    <t>公園へ行きます。</t>
+  </si>
+  <si>
+    <t>We go to the park.</t>
+  </si>
+  <si>
+    <t>我们去公园。</t>
+  </si>
+  <si>
+    <t>우리는 공원에 갑니다.</t>
+  </si>
+  <si>
+    <t>du lịch</t>
+  </si>
+  <si>
+    <t>旅行</t>
+  </si>
+  <si>
+    <t>りょこう</t>
+  </si>
+  <si>
+    <t>travel</t>
+  </si>
+  <si>
+    <t>/ˈtrævəl/</t>
+  </si>
+  <si>
+    <t>lǚxíng</t>
+  </si>
+  <si>
+    <t>여행</t>
+  </si>
+  <si>
+    <t>yeohaeng</t>
+  </si>
+  <si>
+    <t>Tôi thích đi du lịch.</t>
+  </si>
+  <si>
+    <t>旅行が好きです。</t>
+  </si>
+  <si>
+    <t>I like to travel.</t>
+  </si>
+  <si>
+    <t>我喜欢旅行。</t>
+  </si>
+  <si>
+    <t>저는 여행을 좋아합니다.</t>
+  </si>
+  <si>
+    <t>cửa hàng</t>
+  </si>
+  <si>
+    <t>店</t>
+  </si>
+  <si>
+    <t>みせ</t>
+  </si>
+  <si>
+    <t>store</t>
+  </si>
+  <si>
+    <t>/stɔːr/</t>
+  </si>
+  <si>
+    <t>商店</t>
+  </si>
+  <si>
+    <t>shāngdiàn</t>
+  </si>
+  <si>
+    <t>가게</t>
+  </si>
+  <si>
+    <t>gage</t>
+  </si>
+  <si>
+    <t>Tôi vào cửa hàng.</t>
+  </si>
+  <si>
+    <t>店に入ります。</t>
+  </si>
+  <si>
+    <t>I go into the store.</t>
+  </si>
+  <si>
+    <t>我走进商店。</t>
+  </si>
+  <si>
+    <t>가게에 들어갑니다.</t>
+  </si>
+  <si>
+    <t>tiền</t>
+  </si>
+  <si>
+    <t>お金</t>
+  </si>
+  <si>
+    <t>おかね</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>/ˈmʌni/</t>
+  </si>
+  <si>
+    <t>钱</t>
+  </si>
+  <si>
+    <t>qián</t>
+  </si>
+  <si>
+    <t>돈</t>
+  </si>
+  <si>
+    <t>don</t>
+  </si>
+  <si>
+    <t>Tôi có đủ tiền.</t>
+  </si>
+  <si>
+    <t>お金があります。</t>
+  </si>
+  <si>
+    <t>I have enough money.</t>
+  </si>
+  <si>
+    <t>我有足够的钱。</t>
+  </si>
+  <si>
+    <t>돈이 충분합니다.</t>
+  </si>
+  <si>
+    <t>giá cả</t>
+  </si>
+  <si>
+    <t>値段</t>
+  </si>
+  <si>
+    <t>ねだん</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>/praɪs/</t>
+  </si>
+  <si>
+    <t>价格</t>
+  </si>
+  <si>
+    <t>jiàgé</t>
+  </si>
+  <si>
+    <t>가격</t>
+  </si>
+  <si>
+    <t>gagyeok</t>
+  </si>
+  <si>
+    <t>Giá này rất tốt.</t>
+  </si>
+  <si>
+    <t>この値段は安いです。</t>
+  </si>
+  <si>
+    <t>This price is good.</t>
+  </si>
+  <si>
+    <t>这个价格很好。</t>
+  </si>
+  <si>
+    <t>이 가격은 좋습니다.</t>
+  </si>
+  <si>
+    <t>giảm giá</t>
+  </si>
+  <si>
+    <t>割引</t>
+  </si>
+  <si>
+    <t>わりびき</t>
+  </si>
+  <si>
+    <t>discount</t>
+  </si>
+  <si>
+    <t>/ˈdɪskaʊnt/</t>
+  </si>
+  <si>
+    <t>折扣</t>
+  </si>
+  <si>
+    <t>zhékòu</t>
+  </si>
+  <si>
+    <t>할인</t>
+  </si>
+  <si>
+    <t>harin</t>
+  </si>
+  <si>
+    <t>Hôm nay có giảm giá.</t>
+  </si>
+  <si>
+    <t>今日は割引があります。</t>
+  </si>
+  <si>
+    <t>There is a discount today.</t>
+  </si>
+  <si>
+    <t>今天有折扣。</t>
+  </si>
+  <si>
+    <t>오늘은 할인이 있습니다.</t>
+  </si>
+  <si>
+    <t>hóa đơn</t>
+  </si>
+  <si>
+    <t>レシート</t>
+  </si>
+  <si>
+    <t>れしーと</t>
+  </si>
+  <si>
+    <t>receipt</t>
+  </si>
+  <si>
+    <t>/rɪˈsiːt/</t>
+  </si>
+  <si>
+    <t>收据</t>
+  </si>
+  <si>
+    <t>shōujù</t>
+  </si>
+  <si>
+    <t>영수증</t>
+  </si>
+  <si>
+    <t>yeongsujeung</t>
+  </si>
+  <si>
+    <t>Tôi giữ hóa đơn.</t>
+  </si>
+  <si>
+    <t>レシートを持っています。</t>
+  </si>
+  <si>
+    <t>I keep the receipt.</t>
+  </si>
+  <si>
+    <t>我留着收据。</t>
+  </si>
+  <si>
+    <t>영수증을 가지고 있습니다.</t>
+  </si>
+  <si>
+    <t>thẻ</t>
+  </si>
+  <si>
+    <t>カード</t>
+  </si>
+  <si>
+    <t>かーど</t>
+  </si>
+  <si>
+    <t>card</t>
+  </si>
+  <si>
+    <t>/kɑːrd/</t>
+  </si>
+  <si>
+    <t>卡</t>
+  </si>
+  <si>
+    <t>kǎ</t>
+  </si>
+  <si>
+    <t>카드</t>
+  </si>
+  <si>
+    <t>kadeu</t>
+  </si>
+  <si>
+    <t>Tôi trả bằng thẻ.</t>
+  </si>
+  <si>
+    <t>カードで払います。</t>
+  </si>
+  <si>
+    <t>I pay by card.</t>
+  </si>
+  <si>
+    <t>我用卡付款。</t>
+  </si>
+  <si>
+    <t>카드로 계산합니다.</t>
+  </si>
+  <si>
+    <t>tiền mặt</t>
+  </si>
+  <si>
+    <t>現金</t>
+  </si>
+  <si>
+    <t>げんきん</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>/kæʃ/</t>
+  </si>
+  <si>
+    <t>现金</t>
+  </si>
+  <si>
+    <t>xiànjīn</t>
+  </si>
+  <si>
+    <t>현금</t>
+  </si>
+  <si>
+    <t>hyeongeum</t>
+  </si>
+  <si>
+    <t>Tôi có tiền mặt.</t>
+  </si>
+  <si>
+    <t>現金があります。</t>
+  </si>
+  <si>
+    <t>I have cash.</t>
+  </si>
+  <si>
+    <t>我有现金。</t>
+  </si>
+  <si>
+    <t>현금이 있습니다.</t>
+  </si>
+  <si>
+    <t>túi</t>
+  </si>
+  <si>
+    <t>袋</t>
+  </si>
+  <si>
+    <t>ふくろ</t>
+  </si>
+  <si>
+    <t>bag</t>
+  </si>
+  <si>
+    <t>/bæɡ/</t>
+  </si>
+  <si>
+    <t>袋子</t>
+  </si>
+  <si>
+    <t>dàizi</t>
+  </si>
+  <si>
+    <t>봉투</t>
+  </si>
+  <si>
+    <t>bongtu</t>
+  </si>
+  <si>
+    <t>Tôi cần một cái túi.</t>
+  </si>
+  <si>
+    <t>袋をください。</t>
+  </si>
+  <si>
+    <t>I need a bag.</t>
+  </si>
+  <si>
+    <t>请给我一个袋子。</t>
+  </si>
+  <si>
+    <t>봉투 하나 주세요.</t>
+  </si>
+  <si>
+    <t>quần áo</t>
+  </si>
+  <si>
+    <t>服</t>
+  </si>
+  <si>
+    <t>ふく</t>
+  </si>
+  <si>
+    <t>clothes</t>
+  </si>
+  <si>
+    <t>/kloʊðz/</t>
+  </si>
+  <si>
+    <t>衣服</t>
+  </si>
+  <si>
+    <t>yīfu</t>
+  </si>
+  <si>
+    <t>옷</t>
+  </si>
+  <si>
+    <t>ot</t>
+  </si>
+  <si>
+    <t>Tôi thích quần áo này.</t>
+  </si>
+  <si>
+    <t>この服が好きです。</t>
+  </si>
+  <si>
+    <t>I like these clothes.</t>
+  </si>
+  <si>
+    <t>我喜欢这件衣服。</t>
+  </si>
+  <si>
+    <t>이 옷이 마음에 듭니다.</t>
+  </si>
+  <si>
+    <t>giày</t>
+  </si>
+  <si>
+    <t>靴</t>
+  </si>
+  <si>
+    <t>くつ</t>
+  </si>
+  <si>
+    <t>shoes</t>
+  </si>
+  <si>
+    <t>/ʃuːz/</t>
+  </si>
+  <si>
+    <t>鞋</t>
+  </si>
+  <si>
+    <t>xié</t>
+  </si>
+  <si>
+    <t>신발</t>
+  </si>
+  <si>
+    <t>sinbal</t>
+  </si>
+  <si>
+    <t>Tôi muốn mua giày.</t>
+  </si>
+  <si>
+    <t>靴を買いたいです。</t>
+  </si>
+  <si>
+    <t>I want to buy shoes.</t>
+  </si>
+  <si>
+    <t>我想买鞋。</t>
+  </si>
+  <si>
+    <t>신발을 사고 싶습니다.</t>
+  </si>
+  <si>
+    <t>Thời tiết</t>
+  </si>
+  <si>
+    <t>trời</t>
+  </si>
+  <si>
+    <t>空</t>
+  </si>
+  <si>
+    <t>そら</t>
+  </si>
+  <si>
+    <t>sky</t>
+  </si>
+  <si>
+    <t>/skaɪ/</t>
+  </si>
+  <si>
+    <t>天空</t>
+  </si>
+  <si>
+    <t>tiānkōng</t>
+  </si>
+  <si>
+    <t>하늘</t>
+  </si>
+  <si>
+    <t>haneul</t>
+  </si>
+  <si>
+    <t>Bầu trời rất đẹp.</t>
+  </si>
+  <si>
+    <t>空がきれいです。</t>
+  </si>
+  <si>
+    <t>The sky is beautiful.</t>
+  </si>
+  <si>
+    <t>天空很美。</t>
+  </si>
+  <si>
+    <t>하늘이 아름답습니다.</t>
+  </si>
+  <si>
+    <t>mặt trời</t>
+  </si>
+  <si>
+    <t>太陽</t>
+  </si>
+  <si>
+    <t>たいよう</t>
+  </si>
+  <si>
+    <t>sun</t>
+  </si>
+  <si>
+    <t>/sʌn/</t>
+  </si>
+  <si>
+    <t>太阳</t>
+  </si>
+  <si>
+    <t>tàiyáng</t>
+  </si>
+  <si>
+    <t>태양</t>
+  </si>
+  <si>
+    <t>taeyang</t>
+  </si>
+  <si>
+    <t>Mặt trời đang chiếu sáng.</t>
+  </si>
+  <si>
+    <t>太陽が出ています。</t>
+  </si>
+  <si>
+    <t>The sun is shining.</t>
+  </si>
+  <si>
+    <t>太阳出来了。</t>
+  </si>
+  <si>
+    <t>태양이 빛나고 있습니다.</t>
+  </si>
+  <si>
+    <t>mưa</t>
+  </si>
+  <si>
+    <t>雨</t>
+  </si>
+  <si>
+    <t>あめ</t>
+  </si>
+  <si>
+    <t>rain</t>
+  </si>
+  <si>
+    <t>/reɪn/</t>
+  </si>
+  <si>
+    <t>yǔ</t>
+  </si>
+  <si>
+    <t>비</t>
+  </si>
+  <si>
+    <t>bi</t>
+  </si>
+  <si>
+    <t>Hôm nay có mưa.</t>
+  </si>
+  <si>
+    <t>今日は雨です。</t>
+  </si>
+  <si>
+    <t>It is raining today.</t>
+  </si>
+  <si>
+    <t>今天下雨。</t>
+  </si>
+  <si>
+    <t>오늘은 비가 옵니다.</t>
+  </si>
+  <si>
+    <t>tuyết</t>
+  </si>
+  <si>
+    <t>雪</t>
+  </si>
+  <si>
+    <t>ゆき</t>
+  </si>
+  <si>
+    <t>snow</t>
+  </si>
+  <si>
+    <t>/snoʊ/</t>
+  </si>
+  <si>
+    <t>xuě</t>
+  </si>
+  <si>
+    <t>눈</t>
+  </si>
+  <si>
+    <t>nun</t>
+  </si>
+  <si>
+    <t>Mùa đông có tuyết.</t>
+  </si>
+  <si>
+    <t>冬は雪が降ります。</t>
+  </si>
+  <si>
+    <t>It snows in winter.</t>
+  </si>
+  <si>
+    <t>冬天下雪。</t>
+  </si>
+  <si>
+    <t>겨울에는 눈이 옵니다.</t>
+  </si>
+  <si>
+    <t>gió</t>
+  </si>
+  <si>
+    <t>風</t>
+  </si>
+  <si>
+    <t>かぜ</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>/wɪnd/</t>
+  </si>
+  <si>
+    <t>风</t>
+  </si>
+  <si>
+    <t>fēng</t>
+  </si>
+  <si>
+    <t>바람</t>
+  </si>
+  <si>
+    <t>baram</t>
+  </si>
+  <si>
+    <t>Gió hôm nay rất mát.</t>
+  </si>
+  <si>
+    <t>今日は風が気持ちいいです。</t>
+  </si>
+  <si>
+    <t>The wind feels nice today.</t>
+  </si>
+  <si>
+    <t>今天风很舒服。</t>
+  </si>
+  <si>
+    <t>오늘 바람이 시원합니다.</t>
+  </si>
+  <si>
+    <t>mây</t>
+  </si>
+  <si>
+    <t>雲</t>
+  </si>
+  <si>
+    <t>くも</t>
+  </si>
+  <si>
+    <t>cloud</t>
+  </si>
+  <si>
+    <t>/klaʊd/</t>
+  </si>
+  <si>
+    <t>云</t>
+  </si>
+  <si>
+    <t>yún</t>
+  </si>
+  <si>
+    <t>구름</t>
+  </si>
+  <si>
+    <t>gureum</t>
+  </si>
+  <si>
+    <t>Có nhiều mây trên trời.</t>
+  </si>
+  <si>
+    <t>空に雲があります。</t>
+  </si>
+  <si>
+    <t>There are clouds in the sky.</t>
+  </si>
+  <si>
+    <t>天上有云。</t>
+  </si>
+  <si>
+    <t>하늘에 구름이 있습니다.</t>
+  </si>
+  <si>
+    <t>nóng</t>
+  </si>
+  <si>
+    <t>暑い</t>
+  </si>
+  <si>
+    <t>あつい</t>
+  </si>
+  <si>
+    <t>hot</t>
+  </si>
+  <si>
+    <t>/hɑːt/</t>
+  </si>
+  <si>
+    <t>热</t>
+  </si>
+  <si>
+    <t>rè</t>
+  </si>
+  <si>
+    <t>덥다</t>
+  </si>
+  <si>
+    <t>deopda</t>
+  </si>
+  <si>
+    <t>Hôm nay rất nóng.</t>
+  </si>
+  <si>
+    <t>今日は暑いです。</t>
+  </si>
+  <si>
+    <t>It is hot today.</t>
+  </si>
+  <si>
+    <t>今天很热。</t>
+  </si>
+  <si>
+    <t>오늘은 덥습니다.</t>
+  </si>
+  <si>
+    <t>lạnh</t>
+  </si>
+  <si>
+    <t>寒い</t>
+  </si>
+  <si>
+    <t>さむい</t>
+  </si>
+  <si>
+    <t>cold</t>
+  </si>
+  <si>
+    <t>/koʊld/</t>
+  </si>
+  <si>
+    <t>冷</t>
+  </si>
+  <si>
+    <t>lěng</t>
+  </si>
+  <si>
+    <t>춥다</t>
+  </si>
+  <si>
+    <t>chupda</t>
+  </si>
+  <si>
+    <t>Hôm nay khá lạnh.</t>
+  </si>
+  <si>
+    <t>今日は寒いです。</t>
+  </si>
+  <si>
+    <t>It is cold today.</t>
+  </si>
+  <si>
+    <t>今天很冷。</t>
+  </si>
+  <si>
+    <t>오늘은 춥습니다.</t>
+  </si>
+  <si>
+    <t>ấm áp</t>
+  </si>
+  <si>
+    <t>暖かい</t>
+  </si>
+  <si>
+    <t>あたたかい</t>
+  </si>
+  <si>
+    <t>warm</t>
+  </si>
+  <si>
+    <t>/wɔːrm/</t>
+  </si>
+  <si>
+    <t>暖和</t>
+  </si>
+  <si>
+    <t>nuǎnhuo</t>
+  </si>
+  <si>
+    <t>따뜻하다</t>
+  </si>
+  <si>
+    <t>ttatteuthada</t>
+  </si>
+  <si>
+    <t>Mùa xuân rất ấm áp.</t>
+  </si>
+  <si>
+    <t>春は暖かいです。</t>
+  </si>
+  <si>
+    <t>Spring is warm.</t>
+  </si>
+  <si>
+    <t>春天很暖和。</t>
+  </si>
+  <si>
+    <t>봄은 따뜻합니다.</t>
+  </si>
+  <si>
+    <t>trong xanh</t>
+  </si>
+  <si>
+    <t>晴れ</t>
+  </si>
+  <si>
+    <t>はれ</t>
+  </si>
+  <si>
+    <t>sunny</t>
+  </si>
+  <si>
+    <t>/ˈsʌni/</t>
+  </si>
+  <si>
+    <t>晴天</t>
+  </si>
+  <si>
+    <t>qíngtiān</t>
+  </si>
+  <si>
+    <t>맑다</t>
+  </si>
+  <si>
+    <t>malgda</t>
+  </si>
+  <si>
+    <t>Hôm nay trời trong xanh.</t>
+  </si>
+  <si>
+    <t>今日は晴れです。</t>
+  </si>
+  <si>
+    <t>It is sunny today.</t>
+  </si>
+  <si>
+    <t>今天是晴天。</t>
+  </si>
+  <si>
+    <t>오늘은 날씨가 맑습니다.</t>
+  </si>
+  <si>
+    <t>Động vật</t>
+  </si>
+  <si>
+    <t>chó</t>
+  </si>
+  <si>
+    <t>犬</t>
+  </si>
+  <si>
+    <t>いぬ</t>
+  </si>
+  <si>
+    <t>dog</t>
+  </si>
+  <si>
+    <t>/dɔːɡ/</t>
+  </si>
+  <si>
+    <t>狗</t>
+  </si>
+  <si>
+    <t>gǒu</t>
+  </si>
+  <si>
+    <t>개</t>
+  </si>
+  <si>
+    <t>gae</t>
+  </si>
+  <si>
+    <t>Con chó rất đáng yêu.</t>
+  </si>
+  <si>
+    <t>犬はとてもかわいいです。</t>
+  </si>
+  <si>
+    <t>The dog is very cute.</t>
+  </si>
+  <si>
+    <t>这只狗很可爱。</t>
+  </si>
+  <si>
+    <t>강아지가 아주 귀엽습니다.</t>
+  </si>
+  <si>
+    <t>mèo</t>
+  </si>
+  <si>
+    <t>猫</t>
+  </si>
+  <si>
+    <t>ねこ</t>
+  </si>
+  <si>
+    <t>cat</t>
+  </si>
+  <si>
+    <t>/kæt/</t>
+  </si>
+  <si>
+    <t>māo</t>
+  </si>
+  <si>
+    <t>고양이</t>
+  </si>
+  <si>
+    <t>goyangi</t>
+  </si>
+  <si>
+    <t>Con mèo đang ngủ.</t>
+  </si>
+  <si>
+    <t>猫は寝ています。</t>
+  </si>
+  <si>
+    <t>The cat is sleeping.</t>
+  </si>
+  <si>
+    <t>猫在睡觉。</t>
+  </si>
+  <si>
+    <t>고양이가 자고 있습니다.</t>
+  </si>
+  <si>
+    <t>chim</t>
+  </si>
+  <si>
+    <t>鳥</t>
+  </si>
+  <si>
+    <t>とり</t>
+  </si>
+  <si>
+    <t>bird</t>
+  </si>
+  <si>
+    <t>/bɜːrd/</t>
+  </si>
+  <si>
+    <t>鸟</t>
+  </si>
+  <si>
+    <t>niǎo</t>
+  </si>
+  <si>
+    <t>새</t>
+  </si>
+  <si>
+    <t>sae</t>
+  </si>
+  <si>
+    <t>Con chim đang hót.</t>
+  </si>
+  <si>
+    <t>鳥が鳴いています。</t>
+  </si>
+  <si>
+    <t>The bird is singing.</t>
+  </si>
+  <si>
+    <t>鸟在唱歌。</t>
+  </si>
+  <si>
+    <t>새가 노래하고 있습니다.</t>
+  </si>
+  <si>
+    <t>cá</t>
+  </si>
+  <si>
+    <t>魚</t>
+  </si>
+  <si>
+    <t>さかな</t>
+  </si>
+  <si>
+    <t>fish</t>
+  </si>
+  <si>
+    <t>/fɪʃ/</t>
+  </si>
+  <si>
+    <t>鱼</t>
+  </si>
+  <si>
+    <t>yú</t>
+  </si>
+  <si>
+    <t>물고기</t>
+  </si>
+  <si>
+    <t>mulgogi</t>
+  </si>
+  <si>
+    <t>Con cá đang bơi.</t>
+  </si>
+  <si>
+    <t>魚が泳いでいます。</t>
+  </si>
+  <si>
+    <t>The fish is swimming.</t>
+  </si>
+  <si>
+    <t>鱼在游泳。</t>
+  </si>
+  <si>
+    <t>물고기가 헤엄치고 있습니다.</t>
+  </si>
+  <si>
+    <t>thỏ</t>
+  </si>
+  <si>
+    <t>兎</t>
+  </si>
+  <si>
+    <t>うさぎ</t>
+  </si>
+  <si>
+    <t>rabbit</t>
+  </si>
+  <si>
+    <t>/ˈræbɪt/</t>
+  </si>
+  <si>
+    <t>兔子</t>
+  </si>
+  <si>
+    <t>tùzi</t>
+  </si>
+  <si>
+    <t>토끼</t>
+  </si>
+  <si>
+    <t>tokki</t>
+  </si>
+  <si>
+    <t>Con thỏ chạy rất nhanh.</t>
+  </si>
+  <si>
+    <t>兎は速く走ります。</t>
+  </si>
+  <si>
+    <t>The rabbit runs fast.</t>
+  </si>
+  <si>
+    <t>兔子跑得很快。</t>
+  </si>
+  <si>
+    <t>토끼가 빨리 달립니다.</t>
+  </si>
+  <si>
+    <t>ngựa</t>
+  </si>
+  <si>
+    <t>馬</t>
+  </si>
+  <si>
+    <t>うま</t>
+  </si>
+  <si>
+    <t>horse</t>
+  </si>
+  <si>
+    <t>/hɔːrs/</t>
+  </si>
+  <si>
+    <t>马</t>
+  </si>
+  <si>
+    <t>mǎ</t>
+  </si>
+  <si>
+    <t>말</t>
+  </si>
+  <si>
+    <t>mal</t>
+  </si>
+  <si>
+    <t>Con ngựa rất khỏe.</t>
+  </si>
+  <si>
+    <t>馬はとても元気です。</t>
+  </si>
+  <si>
+    <t>The horse is very strong.</t>
+  </si>
+  <si>
+    <t>马很强壮。</t>
+  </si>
+  <si>
+    <t>말은 아주 튼튼합니다.</t>
+  </si>
+  <si>
+    <t>bò</t>
+  </si>
+  <si>
+    <t>牛</t>
+  </si>
+  <si>
+    <t>うし</t>
+  </si>
+  <si>
+    <t>cow</t>
+  </si>
+  <si>
+    <t>/kaʊ/</t>
+  </si>
+  <si>
+    <t>niú</t>
+  </si>
+  <si>
+    <t>소</t>
+  </si>
+  <si>
+    <t>so</t>
+  </si>
+  <si>
+    <t>Con bò đang ăn cỏ.</t>
+  </si>
+  <si>
+    <t>牛は草を食べています。</t>
+  </si>
+  <si>
+    <t>The cow is eating grass.</t>
+  </si>
+  <si>
+    <t>牛在吃草。</t>
+  </si>
+  <si>
+    <t>소가 풀을 먹고 있습니다.</t>
+  </si>
+  <si>
+    <t>hổ</t>
+  </si>
+  <si>
+    <t>虎</t>
+  </si>
+  <si>
+    <t>とら</t>
+  </si>
+  <si>
+    <t>tiger</t>
+  </si>
+  <si>
+    <t>/ˈtaɪɡər/</t>
+  </si>
+  <si>
+    <t>老虎</t>
+  </si>
+  <si>
+    <t>lǎohǔ</t>
+  </si>
+  <si>
+    <t>호랑이</t>
+  </si>
+  <si>
+    <t>horangi</t>
+  </si>
+  <si>
+    <t>Con hổ rất mạnh.</t>
+  </si>
+  <si>
+    <t>虎はとても強いです。</t>
+  </si>
+  <si>
+    <t>The tiger is very strong.</t>
+  </si>
+  <si>
+    <t>老虎很强壮。</t>
+  </si>
+  <si>
+    <t>호랑이는 아주 강합니다.</t>
+  </si>
+  <si>
+    <t>voi</t>
+  </si>
+  <si>
+    <t>象</t>
+  </si>
+  <si>
+    <t>ぞう</t>
+  </si>
+  <si>
+    <t>elephant</t>
+  </si>
+  <si>
+    <t>/ˈelɪfənt/</t>
+  </si>
+  <si>
+    <t>大象</t>
+  </si>
+  <si>
+    <t>dàxiàng</t>
+  </si>
+  <si>
+    <t>코끼리</t>
+  </si>
+  <si>
+    <t>kokkiri</t>
+  </si>
+  <si>
+    <t>Con voi rất to.</t>
+  </si>
+  <si>
+    <t>象はとても大きいです。</t>
+  </si>
+  <si>
+    <t>The elephant is very big.</t>
+  </si>
+  <si>
+    <t>大象很大。</t>
+  </si>
+  <si>
+    <t>코끼리는 아주 큽니다.</t>
+  </si>
+  <si>
+    <t>gấu</t>
+  </si>
+  <si>
+    <t>熊</t>
+  </si>
+  <si>
+    <t>くま</t>
+  </si>
+  <si>
+    <t>bear</t>
+  </si>
+  <si>
+    <t>/ber/</t>
+  </si>
+  <si>
+    <t>xióng</t>
+  </si>
+  <si>
+    <t>곰</t>
+  </si>
+  <si>
+    <t>gom</t>
+  </si>
+  <si>
+    <t>Con gấu rất dễ thương.</t>
+  </si>
+  <si>
+    <t>熊はかわいいです。</t>
+  </si>
+  <si>
+    <t>The bear is cute.</t>
+  </si>
+  <si>
+    <t>熊很可爱。</t>
+  </si>
+  <si>
+    <t>곰은 귀엽습니다.</t>
+  </si>
+  <si>
+    <t>Màu sắc</t>
+  </si>
+  <si>
+    <t>màu đỏ</t>
+  </si>
+  <si>
+    <t>赤</t>
+  </si>
+  <si>
+    <t>あか</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>/red/</t>
+  </si>
+  <si>
+    <t>红色</t>
+  </si>
+  <si>
+    <t>hóngsè</t>
+  </si>
+  <si>
+    <t>빨간색</t>
+  </si>
+  <si>
+    <t>ppalgansaek</t>
+  </si>
+  <si>
+    <t>Tôi thích màu đỏ.</t>
+  </si>
+  <si>
+    <t>赤が好きです。</t>
+  </si>
+  <si>
+    <t>I like red.</t>
+  </si>
+  <si>
+    <t>我喜欢红色。</t>
+  </si>
+  <si>
+    <t>저는 빨간색을 좋아합니다.</t>
+  </si>
+  <si>
+    <t>màu xanh dương</t>
+  </si>
+  <si>
+    <t>青</t>
+  </si>
+  <si>
+    <t>あお</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>/bluː/</t>
+  </si>
+  <si>
+    <t>蓝色</t>
+  </si>
+  <si>
+    <t>lánsè</t>
+  </si>
+  <si>
+    <t>파란색</t>
+  </si>
+  <si>
+    <t>paransaek</t>
+  </si>
+  <si>
+    <t>Bầu trời màu xanh dương.</t>
+  </si>
+  <si>
+    <t>空は青いです。</t>
+  </si>
+  <si>
+    <t>The sky is blue.</t>
+  </si>
+  <si>
+    <t>天空是蓝色的。</t>
+  </si>
+  <si>
+    <t>하늘은 파란색입니다.</t>
+  </si>
+  <si>
+    <t>màu vàng</t>
+  </si>
+  <si>
+    <t>黄色</t>
+  </si>
+  <si>
+    <t>きいろ</t>
+  </si>
+  <si>
+    <t>yellow</t>
+  </si>
+  <si>
+    <t>/ˈjeloʊ/</t>
+  </si>
+  <si>
+    <t>huángsè</t>
+  </si>
+  <si>
+    <t>노란색</t>
+  </si>
+  <si>
+    <t>noransaek</t>
+  </si>
+  <si>
+    <t>Bông hoa màu vàng.</t>
+  </si>
+  <si>
+    <t>花は黄色です。</t>
+  </si>
+  <si>
+    <t>The flower is yellow.</t>
+  </si>
+  <si>
+    <t>花是黄色的。</t>
+  </si>
+  <si>
+    <t>꽃은 노란색입니다.</t>
+  </si>
+  <si>
+    <t>màu xanh lá</t>
+  </si>
+  <si>
+    <t>緑</t>
+  </si>
+  <si>
+    <t>みどり</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>/ɡriːn/</t>
+  </si>
+  <si>
+    <t>绿色</t>
+  </si>
+  <si>
+    <t>lǜsè</t>
+  </si>
+  <si>
+    <t>초록색</t>
+  </si>
+  <si>
+    <t>choroksaek</t>
+  </si>
+  <si>
+    <t>Cây có màu xanh lá.</t>
+  </si>
+  <si>
+    <t>木は緑です。</t>
+  </si>
+  <si>
+    <t>The tree is green.</t>
+  </si>
+  <si>
+    <t>树是绿色的。</t>
+  </si>
+  <si>
+    <t>나무는 초록색입니다.</t>
+  </si>
+  <si>
+    <t>màu trắng</t>
+  </si>
+  <si>
+    <t>白</t>
+  </si>
+  <si>
+    <t>しろ</t>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>/waɪt/</t>
+  </si>
+  <si>
+    <t>白色</t>
+  </si>
+  <si>
+    <t>báisè</t>
+  </si>
+  <si>
+    <t>흰색</t>
+  </si>
+  <si>
+    <t>huinsaek</t>
+  </si>
+  <si>
+    <t>Con mèo màu trắng.</t>
+  </si>
+  <si>
+    <t>猫は白いです。</t>
+  </si>
+  <si>
+    <t>The cat is white.</t>
+  </si>
+  <si>
+    <t>猫是白色的。</t>
+  </si>
+  <si>
+    <t>고양이는 흰색입니다.</t>
+  </si>
+  <si>
+    <t>màu đen</t>
+  </si>
+  <si>
+    <t>黒</t>
+  </si>
+  <si>
+    <t>くろ</t>
+  </si>
+  <si>
+    <t>black</t>
+  </si>
+  <si>
+    <t>/blæk/</t>
+  </si>
+  <si>
+    <t>黑色</t>
+  </si>
+  <si>
+    <t>hēisè</t>
+  </si>
+  <si>
+    <t>검은색</t>
+  </si>
+  <si>
+    <t>geomeunsaek</t>
+  </si>
+  <si>
+    <t>Tôi có một chiếc túi màu đen.</t>
+  </si>
+  <si>
+    <t>黒い袋があります。</t>
+  </si>
+  <si>
+    <t>I have a black bag.</t>
+  </si>
+  <si>
+    <t>我有一个黑色的袋子。</t>
+  </si>
+  <si>
+    <t>검은 가방이 있습니다.</t>
+  </si>
+  <si>
+    <t>màu hồng</t>
+  </si>
+  <si>
+    <t>ピンク</t>
+  </si>
+  <si>
+    <t>ぴんく</t>
+  </si>
+  <si>
+    <t>pink</t>
+  </si>
+  <si>
+    <t>/pɪŋk/</t>
+  </si>
+  <si>
+    <t>粉色</t>
+  </si>
+  <si>
+    <t>fěnsè</t>
+  </si>
+  <si>
+    <t>분홍색</t>
+  </si>
+  <si>
+    <t>bunhongsaek</t>
+  </si>
+  <si>
+    <t>Bông hoa màu hồng rất đẹp.</t>
+  </si>
+  <si>
+    <t>ピンクの花はきれいです。</t>
+  </si>
+  <si>
+    <t>The pink flower is beautiful.</t>
+  </si>
+  <si>
+    <t>粉色的花很漂亮。</t>
+  </si>
+  <si>
+    <t>분홍 꽃이 아름답습니다.</t>
+  </si>
+  <si>
+    <t>màu tím</t>
+  </si>
+  <si>
+    <t>紫</t>
+  </si>
+  <si>
+    <t>むらさき</t>
+  </si>
+  <si>
+    <t>purple</t>
+  </si>
+  <si>
+    <t>/ˈpɜːrpl/</t>
+  </si>
+  <si>
+    <t>紫色</t>
+  </si>
+  <si>
+    <t>zǐsè</t>
+  </si>
+  <si>
+    <t>보라색</t>
+  </si>
+  <si>
+    <t>borasaek</t>
+  </si>
+  <si>
+    <t>Tôi thích màu tím.</t>
+  </si>
+  <si>
+    <t>紫が好きです。</t>
+  </si>
+  <si>
+    <t>I like purple.</t>
+  </si>
+  <si>
+    <t>我喜欢紫色。</t>
+  </si>
+  <si>
+    <t>보라색을 좋아합니다.</t>
+  </si>
+  <si>
+    <t>màu cam</t>
+  </si>
+  <si>
+    <t>オレンジ</t>
+  </si>
+  <si>
+    <t>おれんじ</t>
+  </si>
+  <si>
+    <t>orange</t>
+  </si>
+  <si>
+    <t>/ˈɔːrɪndʒ/</t>
+  </si>
+  <si>
+    <t>橙色</t>
+  </si>
+  <si>
+    <t>chéngsè</t>
+  </si>
+  <si>
+    <t>주황색</t>
+  </si>
+  <si>
+    <t>juhwangsaek</t>
+  </si>
+  <si>
+    <t>Quả cam có màu cam.</t>
+  </si>
+  <si>
+    <t>オレンジはオレンジ色です。</t>
+  </si>
+  <si>
+    <t>The orange is orange.</t>
+  </si>
+  <si>
+    <t>橙子是橙色的。</t>
+  </si>
+  <si>
+    <t>오렌지는 주황색입니다.</t>
+  </si>
+  <si>
+    <t>màu nâu</t>
+  </si>
+  <si>
+    <t>茶色</t>
+  </si>
+  <si>
+    <t>ちゃいろ</t>
+  </si>
+  <si>
+    <t>brown</t>
+  </si>
+  <si>
+    <t>/braʊn/</t>
+  </si>
+  <si>
+    <t>棕色</t>
+  </si>
+  <si>
+    <t>zōngsè</t>
+  </si>
+  <si>
+    <t>갈색</t>
+  </si>
+  <si>
+    <t>galsaek</t>
+  </si>
+  <si>
+    <t>Con gấu màu nâu.</t>
+  </si>
+  <si>
+    <t>熊は茶色です。</t>
+  </si>
+  <si>
+    <t>The bear is brown.</t>
+  </si>
+  <si>
+    <t>熊是棕色的。</t>
+  </si>
+  <si>
+    <t>곰은 갈색입니다.</t>
+  </si>
+  <si>
+    <t>Thể thao</t>
+  </si>
+  <si>
+    <t>thể thao</t>
+  </si>
+  <si>
+    <t>スポーツ</t>
+  </si>
+  <si>
+    <t>すぽーつ</t>
+  </si>
+  <si>
+    <t>sports</t>
+  </si>
+  <si>
+    <t>/spɔːrts/</t>
+  </si>
+  <si>
+    <t>运动</t>
+  </si>
+  <si>
+    <t>yùndòng</t>
+  </si>
+  <si>
+    <t>운동</t>
+  </si>
+  <si>
+    <t>undong</t>
+  </si>
+  <si>
+    <t>Tôi thích thể thao.</t>
+  </si>
+  <si>
+    <t>スポーツが好きです。</t>
+  </si>
+  <si>
+    <t>I like sports.</t>
+  </si>
+  <si>
+    <t>我喜欢运动。</t>
+  </si>
+  <si>
+    <t>저는 운동을 좋아합니다.</t>
+  </si>
+  <si>
+    <t>bóng đá</t>
+  </si>
+  <si>
+    <t>サッカー</t>
+  </si>
+  <si>
+    <t>さっかー</t>
+  </si>
+  <si>
+    <t>soccer</t>
+  </si>
+  <si>
+    <t>/ˈsɑːkər/</t>
+  </si>
+  <si>
+    <t>足球</t>
+  </si>
+  <si>
+    <t>zúqiú</t>
+  </si>
+  <si>
+    <t>축구</t>
+  </si>
+  <si>
+    <t>chukgu</t>
+  </si>
+  <si>
+    <t>Tôi chơi bóng đá.</t>
+  </si>
+  <si>
+    <t>サッカーをします。</t>
+  </si>
+  <si>
+    <t>I play soccer.</t>
+  </si>
+  <si>
+    <t>我踢足球。</t>
+  </si>
+  <si>
+    <t>축구를 합니다.</t>
+  </si>
+  <si>
+    <t>bóng rổ</t>
+  </si>
+  <si>
+    <t>バスケットボール</t>
+  </si>
+  <si>
+    <t>ばすけっとぼーる</t>
+  </si>
+  <si>
+    <t>basketball</t>
+  </si>
+  <si>
+    <t>/ˈbæskɪtbɔːl/</t>
+  </si>
+  <si>
+    <t>篮球</t>
+  </si>
+  <si>
+    <t>lánqiú</t>
+  </si>
+  <si>
+    <t>농구</t>
+  </si>
+  <si>
+    <t>nonggu</t>
+  </si>
+  <si>
+    <t>Anh ấy chơi bóng rổ.</t>
+  </si>
+  <si>
+    <t>彼はバスケットボールをします。</t>
+  </si>
+  <si>
+    <t>He plays basketball.</t>
+  </si>
+  <si>
+    <t>他打篮球。</t>
+  </si>
+  <si>
+    <t>그는 농구를 합니다.</t>
+  </si>
+  <si>
+    <t>bóng chuyền</t>
+  </si>
+  <si>
+    <t>バレーボール</t>
+  </si>
+  <si>
+    <t>ばれーぼーる</t>
+  </si>
+  <si>
+    <t>volleyball</t>
+  </si>
+  <si>
+    <t>/ˈvɑːlibɔːl/</t>
+  </si>
+  <si>
+    <t>排球</t>
+  </si>
+  <si>
+    <t>páiqiú</t>
+  </si>
+  <si>
+    <t>배구</t>
+  </si>
+  <si>
+    <t>baegu</t>
+  </si>
+  <si>
+    <t>Chúng tôi chơi bóng chuyền.</t>
+  </si>
+  <si>
+    <t>私たちはバレーボールをします。</t>
+  </si>
+  <si>
+    <t>We play volleyball.</t>
+  </si>
+  <si>
+    <t>我们打排球。</t>
+  </si>
+  <si>
+    <t>우리는 배구를 합니다.</t>
+  </si>
+  <si>
+    <t>chạy</t>
+  </si>
+  <si>
+    <t>走る</t>
+  </si>
+  <si>
+    <t>はしる</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>/rʌn/</t>
+  </si>
+  <si>
+    <t>跑步</t>
+  </si>
+  <si>
+    <t>pǎobù</t>
+  </si>
+  <si>
+    <t>달리다</t>
+  </si>
+  <si>
+    <t>dallida</t>
+  </si>
+  <si>
+    <t>Tôi chạy mỗi sáng.</t>
+  </si>
+  <si>
+    <t>毎朝走ります。</t>
+  </si>
+  <si>
+    <t>I run every morning.</t>
+  </si>
+  <si>
+    <t>我每天早上跑步。</t>
+  </si>
+  <si>
+    <t>매일 아침 달립니다.</t>
+  </si>
+  <si>
+    <t>bơi</t>
+  </si>
+  <si>
+    <t>泳ぐ</t>
+  </si>
+  <si>
+    <t>およぐ</t>
+  </si>
+  <si>
+    <t>swim</t>
+  </si>
+  <si>
+    <t>/swɪm/</t>
+  </si>
+  <si>
+    <t>游泳</t>
+  </si>
+  <si>
+    <t>yóuyǒng</t>
+  </si>
+  <si>
+    <t>수영하다</t>
+  </si>
+  <si>
+    <t>suyeonghada</t>
+  </si>
+  <si>
+    <t>Tôi thích bơi.</t>
+  </si>
+  <si>
+    <t>泳ぐのが好きです。</t>
+  </si>
+  <si>
+    <t>I like swimming.</t>
+  </si>
+  <si>
+    <t>我喜欢游泳。</t>
+  </si>
+  <si>
+    <t>수영을 좋아합니다.</t>
+  </si>
+  <si>
+    <t>xe đạp</t>
+  </si>
+  <si>
+    <t>自転車</t>
+  </si>
+  <si>
+    <t>じてんしゃ</t>
+  </si>
+  <si>
+    <t>bicycle</t>
+  </si>
+  <si>
+    <t>/ˈbaɪsɪkl/</t>
+  </si>
+  <si>
+    <t>自行车</t>
+  </si>
+  <si>
+    <t>zìxíngchē</t>
+  </si>
+  <si>
+    <t>자전거</t>
+  </si>
+  <si>
+    <t>jajeongeo</t>
+  </si>
+  <si>
+    <t>Tôi đi xe đạp.</t>
+  </si>
+  <si>
+    <t>自転車に乗ります。</t>
+  </si>
+  <si>
+    <t>I ride a bicycle.</t>
+  </si>
+  <si>
+    <t>我骑自行车。</t>
+  </si>
+  <si>
+    <t>자전거를 탑니다.</t>
+  </si>
+  <si>
+    <t>quần vợt</t>
+  </si>
+  <si>
+    <t>テニス</t>
+  </si>
+  <si>
+    <t>てにす</t>
+  </si>
+  <si>
+    <t>tennis</t>
+  </si>
+  <si>
+    <t>/ˈtenɪs/</t>
+  </si>
+  <si>
+    <t>网球</t>
+  </si>
+  <si>
+    <t>wǎngqiú</t>
+  </si>
+  <si>
+    <t>테니스</t>
+  </si>
+  <si>
+    <t>teniseu</t>
+  </si>
+  <si>
+    <t>Tôi chơi quần vợt.</t>
+  </si>
+  <si>
+    <t>テニスをします。</t>
+  </si>
+  <si>
+    <t>I play tennis.</t>
+  </si>
+  <si>
+    <t>我打网球。</t>
+  </si>
+  <si>
+    <t>테니스를 합니다.</t>
+  </si>
+  <si>
+    <t>cầu lông</t>
+  </si>
+  <si>
+    <t>バドミントン</t>
+  </si>
+  <si>
+    <t>ばどみんとん</t>
+  </si>
+  <si>
+    <t>badminton</t>
+  </si>
+  <si>
+    <t>/ˈbædmɪntən/</t>
+  </si>
+  <si>
+    <t>羽毛球</t>
+  </si>
+  <si>
+    <t>yǔmáoqiú</t>
+  </si>
+  <si>
+    <t>배드민턴</t>
+  </si>
+  <si>
+    <t>baedeuminteon</t>
+  </si>
+  <si>
+    <t>Tôi chơi cầu lông.</t>
+  </si>
+  <si>
+    <t>バドミントンをします。</t>
+  </si>
+  <si>
+    <t>I play badminton.</t>
+  </si>
+  <si>
+    <t>我打羽毛球。</t>
+  </si>
+  <si>
+    <t>배드민턴을 합니다.</t>
+  </si>
+  <si>
+    <t>đi bộ</t>
+  </si>
+  <si>
+    <t>歩く</t>
+  </si>
+  <si>
+    <t>あるく</t>
+  </si>
+  <si>
+    <t>walk</t>
+  </si>
+  <si>
+    <t>/wɔːk/</t>
+  </si>
+  <si>
+    <t>散步</t>
+  </si>
+  <si>
+    <t>sànbù</t>
+  </si>
+  <si>
+    <t>걷다</t>
+  </si>
+  <si>
+    <t>geotda</t>
+  </si>
+  <si>
+    <t>Chúng tôi đi bộ trong công viên.</t>
+  </si>
+  <si>
+    <t>公園を歩きます。</t>
+  </si>
+  <si>
+    <t>We walk in the park.</t>
+  </si>
+  <si>
+    <t>我们在公园散步。</t>
+  </si>
+  <si>
+    <t>공원에서 산책합니다.</t>
+  </si>
+  <si>
+    <t>Tình yêu</t>
+  </si>
+  <si>
+    <t>tình yêu</t>
+  </si>
+  <si>
+    <t>愛</t>
+  </si>
+  <si>
+    <t>あい</t>
+  </si>
+  <si>
+    <t>love</t>
+  </si>
+  <si>
+    <t>/lʌv/</t>
+  </si>
+  <si>
+    <t>爱</t>
+  </si>
+  <si>
+    <t>ài</t>
+  </si>
+  <si>
+    <t>사랑</t>
+  </si>
+  <si>
+    <t>sarang</t>
+  </si>
+  <si>
+    <t>Tình yêu làm cuộc sống đẹp hơn.</t>
+  </si>
+  <si>
+    <t>愛は人生を豊かにします。</t>
+  </si>
+  <si>
+    <t>Love makes life beautiful.</t>
+  </si>
+  <si>
+    <t>爱让生活更美好。</t>
+  </si>
+  <si>
+    <t>사랑은 삶을 아름답게 합니다.</t>
+  </si>
+  <si>
+    <t>trái tim</t>
+  </si>
+  <si>
+    <t>心</t>
+  </si>
+  <si>
+    <t>こころ</t>
+  </si>
+  <si>
+    <t>heart</t>
+  </si>
+  <si>
+    <t>/hɑːrt/</t>
+  </si>
+  <si>
+    <t>xīn</t>
+  </si>
+  <si>
+    <t>마음</t>
+  </si>
+  <si>
+    <t>maeum</t>
+  </si>
+  <si>
+    <t>Tôi có một trái tim ấm áp.</t>
+  </si>
+  <si>
+    <t>温かい心があります。</t>
+  </si>
+  <si>
+    <t>I have a warm heart.</t>
+  </si>
+  <si>
+    <t>我有一颗温暖的心。</t>
+  </si>
+  <si>
+    <t>따뜻한 마음이 있습니다.</t>
+  </si>
+  <si>
+    <t>hạnh phúc</t>
+  </si>
+  <si>
+    <t>幸せ</t>
+  </si>
+  <si>
+    <t>しあわせ</t>
+  </si>
+  <si>
+    <t>happiness</t>
+  </si>
+  <si>
+    <t>/ˈhæpinəs/</t>
+  </si>
+  <si>
+    <t>幸福</t>
+  </si>
+  <si>
+    <t>xìngfú</t>
+  </si>
+  <si>
+    <t>행복</t>
+  </si>
+  <si>
+    <t>haengbok</t>
+  </si>
+  <si>
+    <t>Chúng tôi rất hạnh phúc.</t>
+  </si>
+  <si>
+    <t>私たちは幸せです。</t>
+  </si>
+  <si>
+    <t>We are very happy.</t>
+  </si>
+  <si>
+    <t>我们很幸福。</t>
+  </si>
+  <si>
+    <t>우리는 행복합니다.</t>
+  </si>
+  <si>
+    <t>nụ cười</t>
+  </si>
+  <si>
+    <t>笑顔</t>
+  </si>
+  <si>
+    <t>えがお</t>
+  </si>
+  <si>
+    <t>smile</t>
+  </si>
+  <si>
+    <t>/smaɪl/</t>
+  </si>
+  <si>
+    <t>笑容</t>
+  </si>
+  <si>
+    <t>xiàoróng</t>
+  </si>
+  <si>
+    <t>미소</t>
+  </si>
+  <si>
+    <t>miso</t>
+  </si>
+  <si>
+    <t>Nụ cười của bạn rất đẹp.</t>
+  </si>
+  <si>
+    <t>あなたの笑顔はすてきです。</t>
+  </si>
+  <si>
+    <t>Your smile is beautiful.</t>
+  </si>
+  <si>
+    <t>你的笑容很美。</t>
+  </si>
+  <si>
+    <t>당신의 미소는 아름답습니다.</t>
+  </si>
+  <si>
+    <t>bạn</t>
+  </si>
+  <si>
+    <t>友達</t>
+  </si>
+  <si>
+    <t>ともだち</t>
+  </si>
+  <si>
+    <t>friend</t>
+  </si>
+  <si>
+    <t>/frend/</t>
+  </si>
+  <si>
+    <t>朋友</t>
+  </si>
+  <si>
+    <t>péngyou</t>
+  </si>
+  <si>
+    <t>친구</t>
+  </si>
+  <si>
+    <t>chingu</t>
+  </si>
+  <si>
+    <t>Bạn bè rất quan trọng.</t>
+  </si>
+  <si>
+    <t>友達は大切です。</t>
+  </si>
+  <si>
+    <t>Friends are important.</t>
+  </si>
+  <si>
+    <t>朋友很重要。</t>
+  </si>
+  <si>
+    <t>친구는 소중합니다.</t>
+  </si>
+  <si>
+    <t>quà tặng</t>
+  </si>
+  <si>
+    <t>贈り物</t>
+  </si>
+  <si>
+    <t>おくりもの</t>
+  </si>
+  <si>
+    <t>gift</t>
+  </si>
+  <si>
+    <t>/ɡɪft/</t>
+  </si>
+  <si>
+    <t>礼物</t>
+  </si>
+  <si>
+    <t>lǐwù</t>
+  </si>
+  <si>
+    <t>선물</t>
+  </si>
+  <si>
+    <t>seonmul</t>
+  </si>
+  <si>
+    <t>Tôi chuẩn bị một món quà.</t>
+  </si>
+  <si>
+    <t>贈り物を用意します。</t>
+  </si>
+  <si>
+    <t>I prepare a gift.</t>
+  </si>
+  <si>
+    <t>我准备了一份礼物。</t>
+  </si>
+  <si>
+    <t>선물을 준비합니다.</t>
+  </si>
+  <si>
+    <t>hoa</t>
+  </si>
+  <si>
+    <t>花</t>
+  </si>
+  <si>
+    <t>はな</t>
+  </si>
+  <si>
+    <t>flower</t>
+  </si>
+  <si>
+    <t>/ˈflaʊər/</t>
+  </si>
+  <si>
+    <t>huā</t>
+  </si>
+  <si>
+    <t>꽃</t>
+  </si>
+  <si>
+    <t>kkot</t>
+  </si>
+  <si>
+    <t>Bông hoa rất đẹp.</t>
+  </si>
+  <si>
+    <t>花はきれいです。</t>
+  </si>
+  <si>
+    <t>The flower is beautiful.</t>
+  </si>
+  <si>
+    <t>花很漂亮。</t>
+  </si>
+  <si>
+    <t>꽃이 아름답습니다.</t>
+  </si>
+  <si>
+    <t>lời hứa</t>
+  </si>
+  <si>
+    <t>約束</t>
+  </si>
+  <si>
+    <t>やくそく</t>
+  </si>
+  <si>
+    <t>promise</t>
+  </si>
+  <si>
+    <t>/ˈprɑːmɪs/</t>
+  </si>
+  <si>
+    <t>约定</t>
+  </si>
+  <si>
+    <t>yuēdìng</t>
+  </si>
+  <si>
+    <t>약속</t>
+  </si>
+  <si>
+    <t>yaksok</t>
+  </si>
+  <si>
+    <t>Chúng ta giữ lời hứa.</t>
+  </si>
+  <si>
+    <t>約束を守ります。</t>
+  </si>
+  <si>
+    <t>We keep our promise.</t>
+  </si>
+  <si>
+    <t>我们遵守约定。</t>
+  </si>
+  <si>
+    <t>우리는 약속을 지킵니다.</t>
+  </si>
+  <si>
+    <t>cùng nhau</t>
+  </si>
+  <si>
+    <t>一緒</t>
+  </si>
+  <si>
+    <t>いっしょ</t>
+  </si>
+  <si>
+    <t>together</t>
+  </si>
+  <si>
+    <t>/təˈɡeðər/</t>
+  </si>
+  <si>
+    <t>一起</t>
+  </si>
+  <si>
+    <t>yìqǐ</t>
+  </si>
+  <si>
+    <t>함께</t>
+  </si>
+  <si>
+    <t>hamkke</t>
+  </si>
+  <si>
+    <t>Chúng ta cùng nhau đi bộ.</t>
+  </si>
+  <si>
+    <t>一緒に歩きます。</t>
+  </si>
+  <si>
+    <t>We walk together.</t>
+  </si>
+  <si>
+    <t>我们一起散步。</t>
+  </si>
+  <si>
+    <t>함께 걸어갑니다.</t>
+  </si>
+  <si>
+    <t>ước mơ</t>
+  </si>
+  <si>
+    <t>夢</t>
+  </si>
+  <si>
+    <t>ゆめ</t>
+  </si>
+  <si>
+    <t>dream</t>
+  </si>
+  <si>
+    <t>/driːm/</t>
+  </si>
+  <si>
+    <t>梦想</t>
+  </si>
+  <si>
+    <t>mèngxiǎng</t>
+  </si>
+  <si>
+    <t>꿈</t>
+  </si>
+  <si>
+    <t>kkum</t>
+  </si>
+  <si>
+    <t>Chúng tôi có một ước mơ đẹp.</t>
+  </si>
+  <si>
+    <t>すてきな夢があります。</t>
+  </si>
+  <si>
+    <t>We have a beautiful dream.</t>
+  </si>
+  <si>
+    <t>我们有一个美好的梦想。</t>
+  </si>
+  <si>
+    <t>우리는 아름다운 꿈이 있습니다.</t>
   </si>
 </sst>
 </file>
@@ -605,16 +3917,20 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="26" customWidth="1"/>
-    <col min="13" max="14" width="28" customWidth="1"/>
-    <col min="15" max="15" width="26" customWidth="1"/>
-    <col min="16" max="16" width="28" customWidth="1"/>
+    <col min="2" max="2" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.19921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="38" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -927,1523 +4243,4083 @@
       <c r="Q6" s="4"/>
     </row>
     <row r="7" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>107</v>
+      </c>
       <c r="Q7" s="4"/>
     </row>
     <row r="8" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="Q8" s="4"/>
     </row>
     <row r="9" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="Q9" s="4"/>
     </row>
     <row r="10" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>149</v>
+      </c>
       <c r="Q10" s="4"/>
     </row>
     <row r="11" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>163</v>
+      </c>
       <c r="Q11" s="4"/>
     </row>
     <row r="12" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>177</v>
+      </c>
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>191</v>
+      </c>
       <c r="Q13" s="4"/>
     </row>
     <row r="14" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>205</v>
+      </c>
       <c r="Q14" s="4"/>
     </row>
     <row r="15" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>219</v>
+      </c>
       <c r="Q15" s="4"/>
     </row>
     <row r="16" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>233</v>
+      </c>
       <c r="Q16" s="4"/>
     </row>
     <row r="17" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>247</v>
+      </c>
       <c r="Q17" s="4"/>
     </row>
     <row r="18" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>261</v>
+      </c>
       <c r="Q18" s="4"/>
     </row>
     <row r="19" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>275</v>
+      </c>
       <c r="Q19" s="4"/>
     </row>
     <row r="20" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>289</v>
+      </c>
       <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>303</v>
+      </c>
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>317</v>
+      </c>
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>331</v>
+      </c>
       <c r="Q23" s="4"/>
     </row>
     <row r="24" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>345</v>
+      </c>
       <c r="Q24" s="4"/>
     </row>
     <row r="25" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>359</v>
+      </c>
       <c r="Q25" s="4"/>
     </row>
     <row r="26" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
+      <c r="A26" s="4">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>372</v>
+      </c>
       <c r="Q26" s="4"/>
     </row>
     <row r="27" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>386</v>
+      </c>
       <c r="Q27" s="4"/>
     </row>
     <row r="28" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>400</v>
+      </c>
       <c r="Q28" s="4"/>
     </row>
     <row r="29" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>414</v>
+      </c>
       <c r="Q29" s="4"/>
     </row>
     <row r="30" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
+      <c r="A30" s="4">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>428</v>
+      </c>
       <c r="Q30" s="4"/>
     </row>
     <row r="31" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>442</v>
+      </c>
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>456</v>
+      </c>
       <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>470</v>
+      </c>
       <c r="Q33" s="4"/>
     </row>
     <row r="34" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="O34" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>484</v>
+      </c>
       <c r="Q34" s="4"/>
     </row>
     <row r="35" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>498</v>
+      </c>
       <c r="Q35" s="4"/>
     </row>
     <row r="36" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>512</v>
+      </c>
       <c r="Q36" s="4"/>
     </row>
     <row r="37" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>527</v>
+      </c>
       <c r="Q37" s="4"/>
     </row>
     <row r="38" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>541</v>
+      </c>
       <c r="Q38" s="4"/>
     </row>
     <row r="39" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>554</v>
+      </c>
       <c r="Q39" s="4"/>
     </row>
     <row r="40" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
+      <c r="A40" s="4">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>567</v>
+      </c>
       <c r="Q40" s="4"/>
     </row>
     <row r="41" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="O41" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>581</v>
+      </c>
       <c r="Q41" s="4"/>
     </row>
     <row r="42" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
+      <c r="A42" s="4">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>595</v>
+      </c>
       <c r="Q42" s="4"/>
     </row>
     <row r="43" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>609</v>
+      </c>
       <c r="Q43" s="4"/>
     </row>
     <row r="44" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
+      <c r="A44" s="4">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>623</v>
+      </c>
       <c r="Q44" s="4"/>
     </row>
     <row r="45" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
+      <c r="A45" s="4">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>637</v>
+      </c>
       <c r="Q45" s="4"/>
     </row>
     <row r="46" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
+      <c r="A46" s="4">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>651</v>
+      </c>
       <c r="Q46" s="4"/>
     </row>
     <row r="47" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>666</v>
+      </c>
       <c r="Q47" s="4"/>
     </row>
     <row r="48" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
+      <c r="A48" s="4">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>679</v>
+      </c>
       <c r="Q48" s="4"/>
     </row>
     <row r="49" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
+      <c r="A49" s="4">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>693</v>
+      </c>
       <c r="Q49" s="4"/>
     </row>
     <row r="50" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
+      <c r="A50" s="4">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>707</v>
+      </c>
       <c r="Q50" s="4"/>
     </row>
     <row r="51" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
+      <c r="A51" s="4">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>721</v>
+      </c>
       <c r="Q51" s="4"/>
     </row>
     <row r="52" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
+      <c r="A52" s="4">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>735</v>
+      </c>
       <c r="Q52" s="4"/>
     </row>
     <row r="53" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
+      <c r="A53" s="4">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>748</v>
+      </c>
       <c r="Q53" s="4"/>
     </row>
     <row r="54" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
+      <c r="A54" s="4">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="P54" s="4" t="s">
+        <v>762</v>
+      </c>
       <c r="Q54" s="4"/>
     </row>
     <row r="55" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
+      <c r="A55" s="4">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="O55" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>776</v>
+      </c>
       <c r="Q55" s="4"/>
     </row>
     <row r="56" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
+      <c r="A56" s="4">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>789</v>
+      </c>
       <c r="Q56" s="4"/>
     </row>
     <row r="57" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
+      <c r="A57" s="4">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>804</v>
+      </c>
       <c r="Q57" s="4"/>
     </row>
     <row r="58" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
+      <c r="A58" s="4">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="O58" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="P58" s="4" t="s">
+        <v>818</v>
+      </c>
       <c r="Q58" s="4"/>
     </row>
     <row r="59" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
-      <c r="P59" s="4"/>
+      <c r="A59" s="4">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="O59" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="P59" s="4" t="s">
+        <v>831</v>
+      </c>
       <c r="Q59" s="4"/>
     </row>
     <row r="60" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
+      <c r="A60" s="4">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="O60" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="P60" s="4" t="s">
+        <v>845</v>
+      </c>
       <c r="Q60" s="4"/>
     </row>
     <row r="61" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A61" s="4"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
+      <c r="A61" s="4">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="N61" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="O61" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="P61" s="4" t="s">
+        <v>859</v>
+      </c>
       <c r="Q61" s="4"/>
     </row>
     <row r="62" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A62" s="4"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
+      <c r="A62" s="4">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="M62" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="N62" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="O62" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="P62" s="4" t="s">
+        <v>873</v>
+      </c>
       <c r="Q62" s="4"/>
     </row>
     <row r="63" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A63" s="4"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
+      <c r="A63" s="4">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="M63" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="N63" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="O63" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="P63" s="4" t="s">
+        <v>887</v>
+      </c>
       <c r="Q63" s="4"/>
     </row>
     <row r="64" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A64" s="4"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
+      <c r="A64" s="4">
+        <v>63</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="N64" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="O64" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="P64" s="4" t="s">
+        <v>901</v>
+      </c>
       <c r="Q64" s="4"/>
     </row>
     <row r="65" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A65" s="4"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
+      <c r="A65" s="4">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="M65" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="N65" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="O65" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>915</v>
+      </c>
       <c r="Q65" s="4"/>
     </row>
     <row r="66" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
+      <c r="A66" s="4">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="M66" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="N66" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="O66" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="P66" s="4" t="s">
+        <v>929</v>
+      </c>
       <c r="Q66" s="4"/>
     </row>
     <row r="67" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A67" s="4"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
+      <c r="A67" s="4">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="M67" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="N67" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="O67" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="P67" s="4" t="s">
+        <v>944</v>
+      </c>
       <c r="Q67" s="4"/>
     </row>
     <row r="68" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
-      <c r="P68" s="4"/>
+      <c r="A68" s="4">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="M68" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="N68" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="O68" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="P68" s="4" t="s">
+        <v>958</v>
+      </c>
       <c r="Q68" s="4"/>
     </row>
     <row r="69" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
+      <c r="A69" s="4">
+        <v>68</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="N69" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="O69" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="P69" s="4" t="s">
+        <v>972</v>
+      </c>
       <c r="Q69" s="4"/>
     </row>
     <row r="70" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4"/>
+      <c r="A70" s="4">
+        <v>69</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="L70" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="M70" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="N70" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="O70" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="P70" s="4" t="s">
+        <v>986</v>
+      </c>
       <c r="Q70" s="4"/>
     </row>
     <row r="71" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
+      <c r="A71" s="4">
+        <v>70</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="M71" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="N71" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="O71" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="P71" s="4" t="s">
+        <v>1000</v>
+      </c>
       <c r="Q71" s="4"/>
     </row>
     <row r="72" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
+      <c r="A72" s="4">
+        <v>71</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="M72" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="O72" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="P72" s="4" t="s">
+        <v>1014</v>
+      </c>
       <c r="Q72" s="4"/>
     </row>
     <row r="73" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
-      <c r="L73" s="4"/>
-      <c r="M73" s="4"/>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
+      <c r="A73" s="4">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="M73" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="N73" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="O73" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="P73" s="4" t="s">
+        <v>1028</v>
+      </c>
       <c r="Q73" s="4"/>
     </row>
     <row r="74" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
-      <c r="N74" s="4"/>
-      <c r="O74" s="4"/>
-      <c r="P74" s="4"/>
+      <c r="A74" s="4">
+        <v>73</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="L74" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M74" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="N74" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="O74" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P74" s="4" t="s">
+        <v>1042</v>
+      </c>
       <c r="Q74" s="4"/>
     </row>
     <row r="75" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="4"/>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-      <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
+      <c r="A75" s="4">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="M75" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="N75" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="O75" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="P75" s="4" t="s">
+        <v>1056</v>
+      </c>
       <c r="Q75" s="4"/>
     </row>
     <row r="76" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
-      <c r="O76" s="4"/>
-      <c r="P76" s="4"/>
+      <c r="A76" s="4">
+        <v>75</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>1064</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="M76" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="N76" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="O76" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="P76" s="4" t="s">
+        <v>1070</v>
+      </c>
       <c r="Q76" s="4"/>
     </row>
     <row r="77" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4"/>
-      <c r="O77" s="4"/>
-      <c r="P77" s="4"/>
+      <c r="A77" s="4">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M77" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="O77" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="P77" s="4" t="s">
+        <v>1085</v>
+      </c>
       <c r="Q77" s="4"/>
     </row>
     <row r="78" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
-      <c r="O78" s="4"/>
-      <c r="P78" s="4"/>
+      <c r="A78" s="4">
+        <v>77</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="M78" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="O78" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="P78" s="4" t="s">
+        <v>1098</v>
+      </c>
       <c r="Q78" s="4"/>
     </row>
     <row r="79" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
-      <c r="M79" s="4"/>
-      <c r="N79" s="4"/>
-      <c r="O79" s="4"/>
-      <c r="P79" s="4"/>
+      <c r="A79" s="4">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="M79" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="N79" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="O79" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="P79" s="4" t="s">
+        <v>1112</v>
+      </c>
       <c r="Q79" s="4"/>
     </row>
     <row r="80" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
-      <c r="L80" s="4"/>
-      <c r="M80" s="4"/>
-      <c r="N80" s="4"/>
-      <c r="O80" s="4"/>
-      <c r="P80" s="4"/>
+      <c r="A80" s="4">
+        <v>79</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="M80" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="N80" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="O80" s="4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="P80" s="4" t="s">
+        <v>1126</v>
+      </c>
       <c r="Q80" s="4"/>
     </row>
     <row r="81" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
-      <c r="L81" s="4"/>
-      <c r="M81" s="4"/>
-      <c r="N81" s="4"/>
-      <c r="O81" s="4"/>
-      <c r="P81" s="4"/>
+      <c r="A81" s="4">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>1135</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M81" s="4" t="s">
+        <v>1137</v>
+      </c>
+      <c r="N81" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="O81" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="P81" s="4" t="s">
+        <v>1140</v>
+      </c>
       <c r="Q81" s="4"/>
     </row>
     <row r="82" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
-      <c r="L82" s="4"/>
-      <c r="M82" s="4"/>
-      <c r="N82" s="4"/>
-      <c r="O82" s="4"/>
-      <c r="P82" s="4"/>
+      <c r="A82" s="4">
+        <v>81</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="M82" s="4" t="s">
+        <v>1151</v>
+      </c>
+      <c r="N82" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="O82" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="P82" s="4" t="s">
+        <v>1154</v>
+      </c>
       <c r="Q82" s="4"/>
     </row>
     <row r="83" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="4"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
-      <c r="L83" s="4"/>
-      <c r="M83" s="4"/>
-      <c r="N83" s="4"/>
-      <c r="O83" s="4"/>
-      <c r="P83" s="4"/>
+      <c r="A83" s="4">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>1161</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M83" s="4" t="s">
+        <v>1164</v>
+      </c>
+      <c r="N83" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O83" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="P83" s="4" t="s">
+        <v>1167</v>
+      </c>
       <c r="Q83" s="4"/>
     </row>
     <row r="84" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="4"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-      <c r="L84" s="4"/>
-      <c r="M84" s="4"/>
-      <c r="N84" s="4"/>
-      <c r="O84" s="4"/>
-      <c r="P84" s="4"/>
+      <c r="A84" s="4">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>1174</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>1177</v>
+      </c>
+      <c r="M84" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="N84" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="O84" s="4" t="s">
+        <v>1180</v>
+      </c>
+      <c r="P84" s="4" t="s">
+        <v>1181</v>
+      </c>
       <c r="Q84" s="4"/>
     </row>
     <row r="85" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="4"/>
-      <c r="M85" s="4"/>
-      <c r="N85" s="4"/>
-      <c r="O85" s="4"/>
-      <c r="P85" s="4"/>
+      <c r="A85" s="4">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>1186</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>1188</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>1189</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="M85" s="4" t="s">
+        <v>1192</v>
+      </c>
+      <c r="N85" s="4" t="s">
+        <v>1193</v>
+      </c>
+      <c r="O85" s="4" t="s">
+        <v>1194</v>
+      </c>
+      <c r="P85" s="4" t="s">
+        <v>1195</v>
+      </c>
       <c r="Q85" s="4"/>
     </row>
     <row r="86" spans="1:17" ht="27.15" customHeight="1">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="4"/>
-      <c r="L86" s="4"/>
-      <c r="M86" s="4"/>
-      <c r="N86" s="4"/>
-      <c r="O86" s="4"/>
-      <c r="P86" s="4"/>
+      <c r="A86" s="4">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>1200</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>1204</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="M86" s="4" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N86" s="4" t="s">
+        <v>1207</v>
+      </c>
+      <c r="O86" s="4" t="s">
+        <v>1208</v>
+      </c>
+      <c r="P86" s="4" t="s">
+        <v>1209</v>
+      </c>
       <c r="Q86" s="4"/>
     </row>
     <row r="87" spans="1:17" ht="27.15" customHeight="1">
